--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128490593</v>
+        <v>128490450</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568409</v>
+        <v>568361</v>
       </c>
       <c r="R8" t="n">
-        <v>6426421</v>
+        <v>6426412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128490450</v>
+        <v>128490338</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568361</v>
+        <v>568362</v>
       </c>
       <c r="R9" t="n">
-        <v>6426412</v>
+        <v>6426441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128490338</v>
+        <v>128490593</v>
       </c>
       <c r="B10" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568362</v>
+        <v>568409</v>
       </c>
       <c r="R10" t="n">
-        <v>6426441</v>
+        <v>6426421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128490476</v>
+        <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568360</v>
+        <v>568464</v>
       </c>
       <c r="R11" t="n">
-        <v>6426410</v>
+        <v>6426515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490210</v>
+        <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568464</v>
+        <v>568360</v>
       </c>
       <c r="R12" t="n">
-        <v>6426515</v>
+        <v>6426410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
         <v>128490423</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128490305</v>
       </c>
       <c r="B14" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,42 +3016,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490367</v>
+        <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>92770</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3059,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568325</v>
+        <v>568288</v>
       </c>
       <c r="R24" t="n">
-        <v>6426454</v>
+        <v>6426398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490578</v>
+        <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568395</v>
+        <v>568325</v>
       </c>
       <c r="R25" t="n">
-        <v>6426424</v>
+        <v>6426454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,45 +3231,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490410</v>
+        <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>92678</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568288</v>
+        <v>568395</v>
       </c>
       <c r="R26" t="n">
-        <v>6426398</v>
+        <v>6426424</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128490463</v>
+        <v>128490542</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568367</v>
+        <v>568363</v>
       </c>
       <c r="R5" t="n">
-        <v>6426420</v>
+        <v>6426383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128490542</v>
+        <v>128490463</v>
       </c>
       <c r="B6" t="n">
         <v>98571</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568363</v>
+        <v>568367</v>
       </c>
       <c r="R6" t="n">
-        <v>6426383</v>
+        <v>6426420</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128490450</v>
+        <v>128490593</v>
       </c>
       <c r="B8" t="n">
         <v>98571</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568361</v>
+        <v>568409</v>
       </c>
       <c r="R8" t="n">
-        <v>6426412</v>
+        <v>6426421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128490338</v>
+        <v>128490450</v>
       </c>
       <c r="B9" t="n">
         <v>98571</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568362</v>
+        <v>568361</v>
       </c>
       <c r="R9" t="n">
-        <v>6426441</v>
+        <v>6426412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128490593</v>
+        <v>128490338</v>
       </c>
       <c r="B10" t="n">
         <v>98571</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568409</v>
+        <v>568362</v>
       </c>
       <c r="R10" t="n">
-        <v>6426421</v>
+        <v>6426441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490391</v>
+        <v>128490179</v>
       </c>
       <c r="B21" t="n">
         <v>98571</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568320</v>
+        <v>568433</v>
       </c>
       <c r="R21" t="n">
-        <v>6426422</v>
+        <v>6426507</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490179</v>
+        <v>128490391</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568433</v>
+        <v>568320</v>
       </c>
       <c r="R22" t="n">
-        <v>6426507</v>
+        <v>6426422</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,45 +3016,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490410</v>
+        <v>128490367</v>
       </c>
       <c r="B24" t="n">
-        <v>92770</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3062,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568288</v>
+        <v>568325</v>
       </c>
       <c r="R24" t="n">
-        <v>6426398</v>
+        <v>6426454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,7 +3122,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490367</v>
+        <v>128490578</v>
       </c>
       <c r="B25" t="n">
         <v>98571</v>
@@ -3168,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568325</v>
+        <v>568395</v>
       </c>
       <c r="R25" t="n">
-        <v>6426454</v>
+        <v>6426424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,42 +3228,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490578</v>
+        <v>128490410</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>92770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568395</v>
+        <v>568288</v>
       </c>
       <c r="R26" t="n">
-        <v>6426424</v>
+        <v>6426398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128490542</v>
+        <v>128490463</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568363</v>
+        <v>568367</v>
       </c>
       <c r="R5" t="n">
-        <v>6426383</v>
+        <v>6426420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128490463</v>
+        <v>128490542</v>
       </c>
       <c r="B6" t="n">
         <v>98571</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568367</v>
+        <v>568363</v>
       </c>
       <c r="R6" t="n">
-        <v>6426420</v>
+        <v>6426383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3016,42 +3016,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490367</v>
+        <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>92770</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3059,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568325</v>
+        <v>568288</v>
       </c>
       <c r="R24" t="n">
-        <v>6426454</v>
+        <v>6426398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3125,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490578</v>
+        <v>128490367</v>
       </c>
       <c r="B25" t="n">
         <v>98571</v>
@@ -3165,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568395</v>
+        <v>568325</v>
       </c>
       <c r="R25" t="n">
-        <v>6426424</v>
+        <v>6426454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,45 +3231,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490410</v>
+        <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>92770</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568288</v>
+        <v>568395</v>
       </c>
       <c r="R26" t="n">
-        <v>6426398</v>
+        <v>6426424</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128490423</v>
       </c>
       <c r="B13" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128490305</v>
       </c>
       <c r="B14" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490643</v>
+        <v>128490344</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568420</v>
+        <v>568326</v>
       </c>
       <c r="R18" t="n">
-        <v>6426418</v>
+        <v>6426439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490344</v>
+        <v>128490643</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568326</v>
+        <v>568420</v>
       </c>
       <c r="R19" t="n">
-        <v>6426439</v>
+        <v>6426418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490179</v>
+        <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568433</v>
+        <v>568320</v>
       </c>
       <c r="R21" t="n">
-        <v>6426507</v>
+        <v>6426422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490391</v>
+        <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568320</v>
+        <v>568433</v>
       </c>
       <c r="R22" t="n">
-        <v>6426422</v>
+        <v>6426507</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490344</v>
+        <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568326</v>
+        <v>568420</v>
       </c>
       <c r="R18" t="n">
-        <v>6426439</v>
+        <v>6426418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490643</v>
+        <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568420</v>
+        <v>568326</v>
       </c>
       <c r="R19" t="n">
-        <v>6426418</v>
+        <v>6426439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,45 +3016,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490410</v>
+        <v>128490367</v>
       </c>
       <c r="B24" t="n">
-        <v>92782</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3062,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568288</v>
+        <v>568325</v>
       </c>
       <c r="R24" t="n">
-        <v>6426398</v>
+        <v>6426454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490367</v>
+        <v>128490578</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568325</v>
+        <v>568395</v>
       </c>
       <c r="R25" t="n">
-        <v>6426454</v>
+        <v>6426424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,42 +3228,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490578</v>
+        <v>128490410</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>92784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568395</v>
+        <v>568288</v>
       </c>
       <c r="R26" t="n">
-        <v>6426424</v>
+        <v>6426398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,42 +3016,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490367</v>
+        <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3059,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568325</v>
+        <v>568288</v>
       </c>
       <c r="R24" t="n">
-        <v>6426454</v>
+        <v>6426398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490578</v>
+        <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568395</v>
+        <v>568325</v>
       </c>
       <c r="R25" t="n">
-        <v>6426424</v>
+        <v>6426454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,45 +3231,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490410</v>
+        <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>92784</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568288</v>
+        <v>568395</v>
       </c>
       <c r="R26" t="n">
-        <v>6426398</v>
+        <v>6426424</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490643</v>
+        <v>128490344</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568420</v>
+        <v>568326</v>
       </c>
       <c r="R18" t="n">
-        <v>6426418</v>
+        <v>6426439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490344</v>
+        <v>128490643</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568326</v>
+        <v>568420</v>
       </c>
       <c r="R19" t="n">
-        <v>6426439</v>
+        <v>6426418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128490423</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128490305</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490344</v>
+        <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568326</v>
+        <v>568420</v>
       </c>
       <c r="R18" t="n">
-        <v>6426439</v>
+        <v>6426418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490643</v>
+        <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568420</v>
+        <v>568326</v>
       </c>
       <c r="R19" t="n">
-        <v>6426418</v>
+        <v>6426439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128490463</v>
+        <v>128490542</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568367</v>
+        <v>568363</v>
       </c>
       <c r="R5" t="n">
-        <v>6426420</v>
+        <v>6426383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128490542</v>
+        <v>128490463</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568363</v>
+        <v>568367</v>
       </c>
       <c r="R6" t="n">
-        <v>6426383</v>
+        <v>6426420</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,45 +3016,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490410</v>
+        <v>128490578</v>
       </c>
       <c r="B24" t="n">
-        <v>92817</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3062,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568288</v>
+        <v>568395</v>
       </c>
       <c r="R24" t="n">
-        <v>6426398</v>
+        <v>6426424</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3128,7 +3125,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,42 +3228,36 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490578</v>
+        <v>128490410</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>92823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3274,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568395</v>
+        <v>568288</v>
       </c>
       <c r="R26" t="n">
-        <v>6426424</v>
+        <v>6426398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128490542</v>
+        <v>128490463</v>
       </c>
       <c r="B5" t="n">
         <v>98632</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568363</v>
+        <v>568367</v>
       </c>
       <c r="R5" t="n">
-        <v>6426383</v>
+        <v>6426420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128490463</v>
+        <v>128490542</v>
       </c>
       <c r="B6" t="n">
         <v>98632</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568367</v>
+        <v>568363</v>
       </c>
       <c r="R6" t="n">
-        <v>6426420</v>
+        <v>6426383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490578</v>
+        <v>128490367</v>
       </c>
       <c r="B24" t="n">
         <v>98632</v>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568395</v>
+        <v>568325</v>
       </c>
       <c r="R24" t="n">
-        <v>6426424</v>
+        <v>6426454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490367</v>
+        <v>128490578</v>
       </c>
       <c r="B25" t="n">
         <v>98632</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568325</v>
+        <v>568395</v>
       </c>
       <c r="R25" t="n">
-        <v>6426454</v>
+        <v>6426424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128490423</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128490305</v>
       </c>
       <c r="B14" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>128490643</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>128490344</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,42 +3016,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490367</v>
+        <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>92827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3059,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568325</v>
+        <v>568288</v>
       </c>
       <c r="R24" t="n">
-        <v>6426454</v>
+        <v>6426398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490578</v>
+        <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568395</v>
+        <v>568325</v>
       </c>
       <c r="R25" t="n">
-        <v>6426424</v>
+        <v>6426454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,36 +3222,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490410</v>
+        <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568288</v>
+        <v>568395</v>
       </c>
       <c r="R26" t="n">
-        <v>6426398</v>
+        <v>6426424</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128490593</v>
+        <v>128490450</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568409</v>
+        <v>568361</v>
       </c>
       <c r="R8" t="n">
-        <v>6426421</v>
+        <v>6426412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128490450</v>
+        <v>128490338</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568361</v>
+        <v>568362</v>
       </c>
       <c r="R9" t="n">
-        <v>6426412</v>
+        <v>6426441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128490338</v>
+        <v>128490593</v>
       </c>
       <c r="B10" t="n">
         <v>98636</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568362</v>
+        <v>568409</v>
       </c>
       <c r="R10" t="n">
-        <v>6426441</v>
+        <v>6426421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128490210</v>
+        <v>128490476</v>
       </c>
       <c r="B11" t="n">
         <v>98636</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568464</v>
+        <v>568360</v>
       </c>
       <c r="R11" t="n">
-        <v>6426515</v>
+        <v>6426410</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490476</v>
+        <v>128490210</v>
       </c>
       <c r="B12" t="n">
         <v>98636</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568360</v>
+        <v>568464</v>
       </c>
       <c r="R12" t="n">
-        <v>6426410</v>
+        <v>6426515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490391</v>
+        <v>128490179</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568320</v>
+        <v>568433</v>
       </c>
       <c r="R21" t="n">
-        <v>6426422</v>
+        <v>6426507</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490179</v>
+        <v>128490391</v>
       </c>
       <c r="B22" t="n">
         <v>98636</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568433</v>
+        <v>568320</v>
       </c>
       <c r="R22" t="n">
-        <v>6426507</v>
+        <v>6426422</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,36 +3016,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490410</v>
+        <v>128490578</v>
       </c>
       <c r="B24" t="n">
-        <v>92827</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3053,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568288</v>
+        <v>568395</v>
       </c>
       <c r="R24" t="n">
-        <v>6426398</v>
+        <v>6426424</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,42 +3122,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490367</v>
+        <v>128490410</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>92827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568325</v>
+        <v>568288</v>
       </c>
       <c r="R25" t="n">
-        <v>6426454</v>
+        <v>6426398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490578</v>
+        <v>128490367</v>
       </c>
       <c r="B26" t="n">
         <v>98636</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568395</v>
+        <v>568325</v>
       </c>
       <c r="R26" t="n">
-        <v>6426424</v>
+        <v>6426454</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128490450</v>
+        <v>128490593</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568361</v>
+        <v>568409</v>
       </c>
       <c r="R8" t="n">
-        <v>6426412</v>
+        <v>6426421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128490338</v>
+        <v>128490450</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568362</v>
+        <v>568361</v>
       </c>
       <c r="R9" t="n">
-        <v>6426441</v>
+        <v>6426412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128490593</v>
+        <v>128490338</v>
       </c>
       <c r="B10" t="n">
         <v>98636</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568409</v>
+        <v>568362</v>
       </c>
       <c r="R10" t="n">
-        <v>6426421</v>
+        <v>6426441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128490476</v>
+        <v>128490210</v>
       </c>
       <c r="B11" t="n">
         <v>98636</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568360</v>
+        <v>568464</v>
       </c>
       <c r="R11" t="n">
-        <v>6426410</v>
+        <v>6426515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490210</v>
+        <v>128490476</v>
       </c>
       <c r="B12" t="n">
         <v>98636</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568464</v>
+        <v>568360</v>
       </c>
       <c r="R12" t="n">
-        <v>6426515</v>
+        <v>6426410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490179</v>
+        <v>128490391</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568433</v>
+        <v>568320</v>
       </c>
       <c r="R21" t="n">
-        <v>6426507</v>
+        <v>6426422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490391</v>
+        <v>128490179</v>
       </c>
       <c r="B22" t="n">
         <v>98636</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568320</v>
+        <v>568433</v>
       </c>
       <c r="R22" t="n">
-        <v>6426422</v>
+        <v>6426507</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,42 +3016,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490578</v>
+        <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>92827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3059,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568395</v>
+        <v>568288</v>
       </c>
       <c r="R24" t="n">
-        <v>6426424</v>
+        <v>6426398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,36 +3116,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490410</v>
+        <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>92827</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568288</v>
+        <v>568325</v>
       </c>
       <c r="R25" t="n">
-        <v>6426398</v>
+        <v>6426454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128490367</v>
+        <v>128490578</v>
       </c>
       <c r="B26" t="n">
         <v>98636</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568325</v>
+        <v>568395</v>
       </c>
       <c r="R26" t="n">
-        <v>6426454</v>
+        <v>6426424</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128490237</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128490565</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128490225</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128490463</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128490542</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128490086</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128490593</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>128490450</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128490338</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128490210</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128490476</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>128490423</v>
       </c>
       <c r="B13" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>128490305</v>
       </c>
       <c r="B14" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128490164</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>128490123</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490401</v>
+        <v>128490643</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568291</v>
+        <v>568420</v>
       </c>
       <c r="R17" t="n">
-        <v>6426417</v>
+        <v>6426418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490643</v>
+        <v>128490344</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568420</v>
+        <v>568326</v>
       </c>
       <c r="R18" t="n">
-        <v>6426418</v>
+        <v>6426439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490344</v>
+        <v>128490401</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568326</v>
+        <v>568291</v>
       </c>
       <c r="R19" t="n">
-        <v>6426439</v>
+        <v>6426417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>128490290</v>
       </c>
       <c r="B20" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128490391</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>128490179</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>128490192</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>128490410</v>
       </c>
       <c r="B24" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>128490367</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>128490578</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 37524-2025 artfynd.xlsx
+++ b/artfynd/A 37524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128490237</v>
+        <v>128490290</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568417</v>
+        <v>568382</v>
       </c>
       <c r="R2" t="n">
-        <v>6426493</v>
+        <v>6426462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,42 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128490565</v>
+        <v>128490305</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568385</v>
+        <v>568382</v>
       </c>
       <c r="R3" t="n">
-        <v>6426434</v>
+        <v>6426462</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,42 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128490225</v>
+        <v>128490423</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568413</v>
+        <v>568288</v>
       </c>
       <c r="R4" t="n">
-        <v>6426540</v>
+        <v>6426398</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +984,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128490463</v>
+        <v>128490086</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568367</v>
+        <v>568425</v>
       </c>
       <c r="R5" t="n">
-        <v>6426420</v>
+        <v>6426542</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128490542</v>
+        <v>128490123</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568363</v>
+        <v>568442</v>
       </c>
       <c r="R6" t="n">
-        <v>6426383</v>
+        <v>6426518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128490086</v>
+        <v>128490164</v>
       </c>
       <c r="B7" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568425</v>
+        <v>568415</v>
       </c>
       <c r="R7" t="n">
-        <v>6426542</v>
+        <v>6426529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128490593</v>
+        <v>128490179</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568409</v>
+        <v>568433</v>
       </c>
       <c r="R8" t="n">
-        <v>6426421</v>
+        <v>6426507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128490450</v>
+        <v>128490192</v>
       </c>
       <c r="B9" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568361</v>
+        <v>568472</v>
       </c>
       <c r="R9" t="n">
-        <v>6426412</v>
+        <v>6426528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128490338</v>
+        <v>128490210</v>
       </c>
       <c r="B10" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568362</v>
+        <v>568464</v>
       </c>
       <c r="R10" t="n">
-        <v>6426441</v>
+        <v>6426515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128490210</v>
+        <v>128490225</v>
       </c>
       <c r="B11" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568464</v>
+        <v>568413</v>
       </c>
       <c r="R11" t="n">
-        <v>6426515</v>
+        <v>6426540</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490476</v>
+        <v>128490237</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568360</v>
+        <v>568417</v>
       </c>
       <c r="R12" t="n">
-        <v>6426410</v>
+        <v>6426493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,46 +1850,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490423</v>
+        <v>128490338</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,13 +1893,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568288</v>
+        <v>568362</v>
       </c>
       <c r="R13" t="n">
-        <v>6426398</v>
+        <v>6426441</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,6 +1937,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1950,46 +1956,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128490305</v>
+        <v>128490344</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1997,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568382</v>
+        <v>568326</v>
       </c>
       <c r="R14" t="n">
-        <v>6426462</v>
+        <v>6426439</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2041,6 +2043,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2059,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128490164</v>
+        <v>128490367</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568415</v>
+        <v>568325</v>
       </c>
       <c r="R15" t="n">
-        <v>6426529</v>
+        <v>6426454</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128490123</v>
+        <v>128490391</v>
       </c>
       <c r="B16" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568442</v>
+        <v>568320</v>
       </c>
       <c r="R16" t="n">
-        <v>6426518</v>
+        <v>6426422</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2277,7 @@
         <v>128490401</v>
       </c>
       <c r="B17" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490643</v>
+        <v>128490450</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568420</v>
+        <v>568361</v>
       </c>
       <c r="R18" t="n">
-        <v>6426418</v>
+        <v>6426412</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490344</v>
+        <v>128490463</v>
       </c>
       <c r="B19" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568326</v>
+        <v>568367</v>
       </c>
       <c r="R19" t="n">
-        <v>6426439</v>
+        <v>6426420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,45 +2592,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128490290</v>
+        <v>128490476</v>
       </c>
       <c r="B20" t="n">
-        <v>92148</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568382</v>
+        <v>568360</v>
       </c>
       <c r="R20" t="n">
-        <v>6426462</v>
+        <v>6426410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490391</v>
+        <v>128490542</v>
       </c>
       <c r="B21" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568320</v>
+        <v>568363</v>
       </c>
       <c r="R21" t="n">
-        <v>6426422</v>
+        <v>6426383</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490179</v>
+        <v>128490565</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568433</v>
+        <v>568385</v>
       </c>
       <c r="R22" t="n">
-        <v>6426507</v>
+        <v>6426434</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490192</v>
+        <v>128490578</v>
       </c>
       <c r="B23" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568472</v>
+        <v>568395</v>
       </c>
       <c r="R23" t="n">
-        <v>6426528</v>
+        <v>6426424</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,36 +3016,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490410</v>
+        <v>128490593</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3053,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568288</v>
+        <v>568409</v>
       </c>
       <c r="R24" t="n">
-        <v>6426398</v>
+        <v>6426421</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490367</v>
+        <v>128490643</v>
       </c>
       <c r="B25" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3159,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568325</v>
+        <v>568420</v>
       </c>
       <c r="R25" t="n">
-        <v>6426454</v>
+        <v>6426418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,112 +3225,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>128490578</v>
-      </c>
-      <c r="B26" t="n">
-        <v>98646</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>A 37524, Kristgöl, Sm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>568395</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6426424</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
